--- a/artfynd/A 45296-2020 artfynd.xlsx
+++ b/artfynd/A 45296-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45296-2020 artfynd.xlsx
+++ b/artfynd/A 45296-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1050,6 +1050,123 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118860937</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102885</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>706</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svedjenäva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Geranium bohemicum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skillnaden (Skillnaden), Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>640523</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6530277</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Västerljung</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hygge Sörmlandsleden mot Ringsjön</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gitte Jutvik Guterstam</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gitte Jutvik Guterstam</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45296-2020 artfynd.xlsx
+++ b/artfynd/A 45296-2020 artfynd.xlsx
@@ -1055,7 +1055,7 @@
         <v>118860937</v>
       </c>
       <c r="B5" t="n">
-        <v>102885</v>
+        <v>102892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 45296-2020 artfynd.xlsx
+++ b/artfynd/A 45296-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,6 +1167,130 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120369921</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102975</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>706</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svedjenäva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Geranium bohemicum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sörmlandsleden SO Oskarshäll, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>640536</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6530259</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Västerljung</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Återfynd</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45296-2020 artfynd.xlsx
+++ b/artfynd/A 45296-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1291,6 +1291,140 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122392166</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56584</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Källvikskorset, Ringsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>640790</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6530200</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Trosa</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Västerljung</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Blandskog med mycket gran, hygge intill</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gunilla Thyreen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gunilla Thyreen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45296-2020 artfynd.xlsx
+++ b/artfynd/A 45296-2020 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>122392166</v>
       </c>
       <c r="B7" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 45296-2020 artfynd.xlsx
+++ b/artfynd/A 45296-2020 artfynd.xlsx
@@ -1311,11 +1311,6 @@
       <c r="E7" t="n">
         <v>100138</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Tetrao urogallus</t>

--- a/artfynd/A 45296-2020 artfynd.xlsx
+++ b/artfynd/A 45296-2020 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>122392166</v>
       </c>
       <c r="B7" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,6 +1310,11 @@
       </c>
       <c r="E7" t="n">
         <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 45296-2020 artfynd.xlsx
+++ b/artfynd/A 45296-2020 artfynd.xlsx
@@ -1296,7 +1296,7 @@
         <v>122392166</v>
       </c>
       <c r="B7" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
